--- a/hvac_troubleshooting_template.xlsx
+++ b/hvac_troubleshooting_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SESA539153\Desktop\Converter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{871639EC-6A1C-4A4D-87D0-E11FD4D42793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA7C29F-375D-44D1-989B-249EA1E53FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9570" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Troubleshooting Template" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Connect to the AS</t>
+  </si>
+  <si>
+    <t>q</t>
   </si>
 </sst>
 </file>
@@ -839,7 +842,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
@@ -859,7 +862,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
